--- a/config/tickers.xlsx
+++ b/config/tickers.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="46">
   <si>
     <t>Ticker</t>
   </si>
@@ -511,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -524,329 +524,25 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" t="s">
         <v>5</v>
       </c>
     </row>

--- a/config/tickers.xlsx
+++ b/config/tickers.xlsx
@@ -14,13 +14,14 @@
   <sheets>
     <sheet name="Selected_Stocks" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="47">
   <si>
     <t>Ticker</t>
   </si>
@@ -158,6 +159,9 @@
   </si>
   <si>
     <t>OLFI</t>
+  </si>
+  <si>
+    <t>SIPC</t>
   </si>
 </sst>
 </file>
@@ -511,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -524,26 +528,338 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -895,4 +1211,46 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/config/tickers.xlsx
+++ b/config/tickers.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="51">
   <si>
     <t>Ticker</t>
   </si>
@@ -162,6 +162,18 @@
   </si>
   <si>
     <t>SIPC</t>
+  </si>
+  <si>
+    <t>BONY</t>
+  </si>
+  <si>
+    <t>MBSC</t>
+  </si>
+  <si>
+    <t>ATQA</t>
+  </si>
+  <si>
+    <t>ISMQ</t>
   </si>
 </sst>
 </file>
@@ -515,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -862,8 +874,41 @@
         <v>4</v>
       </c>
     </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
